--- a/data_folder/bev_electronics_wiring/input_data/case.xlsx
+++ b/data_folder/bev_electronics_wiring/input_data/case.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,11 +613,6 @@
           <t>TC_target_layer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_residual</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -637,7 +632,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_alalloy_general</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -652,7 +647,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>F_collected</t>
+          <t>F_alalloy_general</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -684,7 +679,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_alalloy_own</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -699,7 +694,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>F_dismantled</t>
+          <t>F_alalloy_own</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -710,11 +705,6 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>material</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -731,7 +721,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_collected</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -746,7 +736,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>F_loss_separation</t>
+          <t>F_collected</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -757,11 +747,6 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>element</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -773,12 +758,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_cu_general</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>F_loss_shredding</t>
+          <t>F_cu_general</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -790,12 +775,12 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_cu_own</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>F_not_dismantled</t>
+          <t>F_cu_own</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -807,12 +792,12 @@
     <row r="7">
       <c r="D7" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>F_recovered_al_alloy</t>
+          <t>F_disassembled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -824,34 +809,70 @@
     <row r="8">
       <c r="D8" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_fealloy_general</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>F_recovered_cu</t>
+          <t>F_fealloy_general</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="D9" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_fealloy_own</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>F_recovered_fe_alloy</t>
+          <t>F_fealloy_own</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="D10" t="inlineStr">
         <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F_in_car</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F_loss_own</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
           <t>F_shredded</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>F_shredded</t>
         </is>
@@ -1285,18 +1306,18 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1392,10 +1413,8 @@
           <t>Motors</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="G2" t="n">
+        <v>0.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1454,10 +1473,8 @@
           <t>Motors</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0.15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1516,10 +1533,8 @@
           <t>Motors</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -1570,10 +1585,8 @@
           <t>Wiring</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="G5" t="n">
+        <v>0.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1632,10 +1645,8 @@
           <t>Wiring</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
+      <c r="G6" t="n">
+        <v>0.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1694,10 +1705,8 @@
           <t>Wiring</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -1748,10 +1757,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="G8" t="n">
+        <v>0.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1810,10 +1817,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="G9" t="n">
+        <v>0.05</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1872,10 +1877,8 @@
           <t>alalloy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+      <c r="G10" t="n">
+        <v>0.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1934,10 +1937,8 @@
           <t>alalloy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="G11" t="n">
+        <v>0.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1996,10 +1997,8 @@
           <t>fealloy</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="G12" t="n">
+        <v>0.95</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2058,10 +2057,8 @@
           <t>fealloy</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="G13" t="n">
+        <v>0.05</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2120,10 +2117,8 @@
           <t>rest</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G14" t="n">
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2169,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="G15" t="n">
+        <v>0.95</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2236,10 +2229,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+      <c r="G16" t="n">
+        <v>0.05</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2298,10 +2289,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="G17" t="n">
+        <v>0.55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2360,10 +2349,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
+      <c r="G18" t="n">
+        <v>0.45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2422,10 +2409,8 @@
           <t>alalloy</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
+      <c r="G19" t="n">
+        <v>0.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2484,10 +2469,8 @@
           <t>alalloy</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="G20" t="n">
+        <v>0.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2546,10 +2529,8 @@
           <t>fealloy</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+      <c r="G21" t="n">
+        <v>0.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2608,10 +2589,8 @@
           <t>fealloy</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="G22" t="n">
+        <v>0.1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2670,10 +2649,8 @@
           <t>rest</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -2724,10 +2701,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="G24" t="n">
+        <v>0.55</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2786,10 +2761,8 @@
           <t>copper</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
+      <c r="G25" t="n">
+        <v>0.45</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2818,6 +2791,26 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="A2:A25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$D$2:$D$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$E$2:$E$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$F$2:$F$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$G$2:$G$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$H$2:$H$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+      <formula1>=_lists!$I$2:$I$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_folder/bev_electronics_wiring/input_data/case.xlsx
+++ b/data_folder/bev_electronics_wiring/input_data/case.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rm/Documents/GitHub/RAWCLICRecoveryModel/data_folder/bev_electronics_wiring/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5244696D-EBBC-EF41-88AC-193945724C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF2D7A5-1D07-7E4C-A7AA-19E9D49675BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51300" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="45900" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="TCs" sheetId="4" r:id="rId4"/>
     <sheet name="TCs_improved" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1247,13 +1260,13 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -1282,13 +1295,13 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H3">
+        <v>0.2</v>
+      </c>
+      <c r="I3">
         <v>0.5</v>
-      </c>
-      <c r="I3">
-        <v>0.85</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -1355,13 +1368,13 @@
         <v>25</v>
       </c>
       <c r="G5">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="I5">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -1390,7 +1403,7 @@
         <v>25</v>
       </c>
       <c r="G6">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H6">
         <v>0.05</v>
@@ -1463,13 +1476,13 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>0.7</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="H8">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I8">
-        <v>0.85</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J8" t="s">
         <v>29</v>
@@ -1498,13 +1511,13 @@
         <v>28</v>
       </c>
       <c r="G9">
+        <v>0.154</v>
+      </c>
+      <c r="H9">
+        <v>0.05</v>
+      </c>
+      <c r="I9">
         <v>0.3</v>
-      </c>
-      <c r="H9">
-        <v>0.15</v>
-      </c>
-      <c r="I9">
-        <v>0.65</v>
       </c>
       <c r="J9" t="s">
         <v>29</v>
@@ -1533,13 +1546,13 @@
         <v>33</v>
       </c>
       <c r="G10">
-        <v>0.7</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="H10">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I10">
-        <v>0.85</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J10" t="s">
         <v>29</v>
@@ -1568,13 +1581,13 @@
         <v>33</v>
       </c>
       <c r="G11">
+        <v>0.154</v>
+      </c>
+      <c r="H11">
+        <v>0.05</v>
+      </c>
+      <c r="I11">
         <v>0.3</v>
-      </c>
-      <c r="H11">
-        <v>0.15</v>
-      </c>
-      <c r="I11">
-        <v>0.65</v>
       </c>
       <c r="J11" t="s">
         <v>29</v>
@@ -1603,13 +1616,13 @@
         <v>35</v>
       </c>
       <c r="G12">
-        <v>0.7</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="H12">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I12">
-        <v>0.85</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="J12" t="s">
         <v>29</v>
@@ -1638,13 +1651,13 @@
         <v>35</v>
       </c>
       <c r="G13">
+        <v>0.154</v>
+      </c>
+      <c r="H13">
+        <v>0.05</v>
+      </c>
+      <c r="I13">
         <v>0.3</v>
-      </c>
-      <c r="H13">
-        <v>0.15</v>
-      </c>
-      <c r="I13">
-        <v>0.65</v>
       </c>
       <c r="J13" t="s">
         <v>29</v>
@@ -1711,13 +1724,13 @@
         <v>28</v>
       </c>
       <c r="G15">
-        <v>0.85</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="H15">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="I15">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="J15" t="s">
         <v>29</v>
@@ -1746,13 +1759,13 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>0.15</v>
+        <v>5.5E-2</v>
       </c>
       <c r="H16">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I16">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="s">
         <v>29</v>
@@ -2029,13 +2042,13 @@
         <v>28</v>
       </c>
       <c r="G24">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I24">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="s">
         <v>39</v>
@@ -2064,10 +2077,10 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I25">
         <v>0.65</v>
@@ -2151,13 +2164,13 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I2">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
@@ -2186,13 +2199,13 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="I3">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="J3" t="s">
         <v>18</v>
@@ -2259,13 +2272,13 @@
         <v>25</v>
       </c>
       <c r="G5">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="I5">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -2294,13 +2307,13 @@
         <v>25</v>
       </c>
       <c r="G6">
+        <v>0.04</v>
+      </c>
+      <c r="H6">
+        <v>0.01</v>
+      </c>
+      <c r="I6">
         <v>0.15</v>
-      </c>
-      <c r="H6">
-        <v>0.05</v>
-      </c>
-      <c r="I6">
-        <v>0.25</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
@@ -2367,13 +2380,13 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>0.7</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="H8">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I8">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J8" t="s">
         <v>29</v>
@@ -2402,13 +2415,13 @@
         <v>28</v>
       </c>
       <c r="G9">
-        <v>0.3</v>
+        <v>6.2E-2</v>
       </c>
       <c r="H9">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I9">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="s">
         <v>29</v>
@@ -2437,13 +2450,13 @@
         <v>33</v>
       </c>
       <c r="G10">
-        <v>0.7</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="H10">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I10">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J10" t="s">
         <v>29</v>
@@ -2472,13 +2485,13 @@
         <v>33</v>
       </c>
       <c r="G11">
-        <v>0.3</v>
+        <v>6.2E-2</v>
       </c>
       <c r="H11">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I11">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="s">
         <v>29</v>
@@ -2507,13 +2520,13 @@
         <v>35</v>
       </c>
       <c r="G12">
-        <v>0.7</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="H12">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I12">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J12" t="s">
         <v>29</v>
@@ -2542,13 +2555,13 @@
         <v>35</v>
       </c>
       <c r="G13">
-        <v>0.3</v>
+        <v>6.2E-2</v>
       </c>
       <c r="H13">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I13">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="s">
         <v>29</v>
@@ -2615,13 +2628,13 @@
         <v>28</v>
       </c>
       <c r="G15">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="H15">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="I15">
-        <v>0.95</v>
+        <v>0.995</v>
       </c>
       <c r="J15" t="s">
         <v>29</v>
@@ -2650,13 +2663,13 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="H16">
+        <v>1E-3</v>
+      </c>
+      <c r="I16">
         <v>0.05</v>
-      </c>
-      <c r="I16">
-        <v>0.3</v>
       </c>
       <c r="J16" t="s">
         <v>29</v>
@@ -2685,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="G17">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="H17">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="I17">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="J17" t="s">
         <v>39</v>
@@ -2720,13 +2733,13 @@
         <v>28</v>
       </c>
       <c r="G18">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H18">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I18">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="s">
         <v>39</v>
@@ -2755,13 +2768,13 @@
         <v>33</v>
       </c>
       <c r="G19">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H19">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I19">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
@@ -2790,13 +2803,13 @@
         <v>33</v>
       </c>
       <c r="G20">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H20">
+        <v>0.1</v>
+      </c>
+      <c r="I20">
         <v>0.5</v>
-      </c>
-      <c r="H20">
-        <v>0.35</v>
-      </c>
-      <c r="I20">
-        <v>0.7</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -2825,13 +2838,13 @@
         <v>35</v>
       </c>
       <c r="G21">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H21">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I21">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
@@ -2860,13 +2873,13 @@
         <v>35</v>
       </c>
       <c r="G22">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H22">
+        <v>0.1</v>
+      </c>
+      <c r="I22">
         <v>0.5</v>
-      </c>
-      <c r="H22">
-        <v>0.35</v>
-      </c>
-      <c r="I22">
-        <v>0.7</v>
       </c>
       <c r="J22" t="s">
         <v>39</v>
@@ -2933,13 +2946,13 @@
         <v>28</v>
       </c>
       <c r="G24">
-        <v>0.55000000000000004</v>
+        <v>0.85</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="I24">
-        <v>0.75</v>
+        <v>0.94</v>
       </c>
       <c r="J24" t="s">
         <v>39</v>
@@ -2968,13 +2981,13 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="I25">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="s">
         <v>39</v>
